--- a/UTCUTS/A1_Outputs/previous_version_1/A-O_AR_Projections_PREV1.xlsx
+++ b/UTCUTS/A1_Outputs/previous_version_1/A-O_AR_Projections_PREV1.xlsx
@@ -12932,7 +12932,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE8C3A73-66AB-4737-8478-787F0589AFCF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C0B1C2A-8253-4D4C-A066-EDFDF302029B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
